--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/one_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/one_shot/EVAL_SUMMARY.xlsx
@@ -541,10 +541,10 @@
         <v>131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.468085</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N2" t="n">
         <v>0.22</v>
@@ -600,13 +600,13 @@
         <v>131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.458333</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.218906</v>
       </c>
       <c r="O3" t="n">
         <v>0.6860000000000001</v>
@@ -659,13 +659,13 @@
         <v>131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.458333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.218906</v>
       </c>
       <c r="O4" t="n">
         <v>0.6860000000000001</v>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.461538</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2192691029900332</v>
+        <v>0.219269</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.686667</v>
       </c>
       <c r="J2" t="n">
         <v>1500</v>
